--- a/data/raw/Giá vốn theo sp.xlsx
+++ b/data/raw/Giá vốn theo sp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quang\OneDrive\Desktop\DuAnTotNghiep\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046AEF8D-6E42-41F3-A71D-1229DCA63FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3D5B5B-A8D0-4886-9289-895AA328A9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BB04D76-5AD4-4B34-964C-F376ACF32298}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="506">
   <si>
     <t>Mã Sản phẩm</t>
   </si>
@@ -1562,6 +1562,9 @@
   </si>
   <si>
     <t>Ground Coffee 053</t>
+  </si>
+  <si>
+    <t>251999.99948000003</t>
   </si>
 </sst>
 </file>
@@ -1581,15 +1584,21 @@
       <name val="VNI-Times"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1597,14 +1606,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1955,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA404BBC-48D6-4950-B001-20681BA45B9F}">
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:M243"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -1964,9 +1987,10 @@
     <col min="4" max="4" width="11.77734375" customWidth="1"/>
     <col min="5" max="5" width="11.109375" customWidth="1"/>
     <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="15" max="15" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1986,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2006,7 +2030,7 @@
         <v>49041</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2025,8 +2049,9 @@
       <c r="F3" s="1">
         <v>124470</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2045,8 +2070,9 @@
       <c r="F4" s="1">
         <v>14386</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2065,8 +2091,9 @@
       <c r="F5" s="1">
         <v>27583</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2085,8 +2112,9 @@
       <c r="F6" s="1">
         <v>28448</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2105,8 +2133,9 @@
       <c r="F7" s="1">
         <v>28354</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2125,8 +2154,9 @@
       <c r="F8" s="1">
         <v>54141</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -2145,8 +2175,9 @@
       <c r="F9" s="1">
         <v>23832</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2165,8 +2196,9 @@
       <c r="F10" s="1">
         <v>60342</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2185,8 +2217,9 @@
       <c r="F11" s="1">
         <v>23542</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2206,7 +2239,7 @@
         <v>160965</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2226,7 +2259,7 @@
         <v>23397</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -2246,7 +2279,7 @@
         <v>107093</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2266,7 +2299,7 @@
         <v>45501</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -4317,10 +4350,11 @@
         <v>244</v>
       </c>
       <c r="E115">
-        <v>2000</v>
+        <v>51499.999640000002</v>
       </c>
       <c r="F115" s="1">
-        <v>994</v>
+        <f>0.45*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>23174.999838</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4596,11 +4630,12 @@
       <c r="D129" t="s">
         <v>272</v>
       </c>
-      <c r="E129">
-        <v>2000</v>
+      <c r="E129" s="4" t="s">
+        <v>505</v>
       </c>
       <c r="F129" s="1">
-        <v>1593</v>
+        <f>0.45*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>113399.99976600001</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4656,11 +4691,12 @@
       <c r="D132" t="s">
         <v>278</v>
       </c>
-      <c r="E132">
-        <v>2000</v>
+      <c r="E132" s="3">
+        <v>343000.00027999998</v>
       </c>
       <c r="F132" s="1">
-        <v>1532</v>
+        <f>0.45*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>154350.000126</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4676,11 +4712,12 @@
       <c r="D133" t="s">
         <v>280</v>
       </c>
-      <c r="E133">
-        <v>2000</v>
+      <c r="E133" s="3">
+        <v>464000.00024000002</v>
       </c>
       <c r="F133" s="1">
-        <v>1547</v>
+        <f>0.55*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>255200.00013200004</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4736,11 +4773,12 @@
       <c r="D136" t="s">
         <v>286</v>
       </c>
-      <c r="E136">
-        <v>2000</v>
+      <c r="E136" s="2">
+        <v>574000.00040000002</v>
       </c>
       <c r="F136" s="1">
-        <v>1551</v>
+        <f>0.55*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>315700.00022000005</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4796,11 +4834,12 @@
       <c r="D139" t="s">
         <v>292</v>
       </c>
-      <c r="E139">
-        <v>2000</v>
+      <c r="E139" s="2">
+        <v>362000</v>
       </c>
       <c r="F139" s="1">
-        <v>1537</v>
+        <f>0.45*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>162900</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4816,11 +4855,12 @@
       <c r="D140" t="s">
         <v>294</v>
       </c>
-      <c r="E140">
-        <v>2000</v>
+      <c r="E140" s="2">
+        <v>364999.99988000002</v>
       </c>
       <c r="F140" s="1">
-        <v>1570</v>
+        <f>0.45*Table2[[#This Row],[Giá bán lẻ]]</f>
+        <v>164249.99994600003</v>
       </c>
     </row>
     <row r="141" spans="1:6">
